--- a/RTO AMOUNT CALCULATOR.xlsx
+++ b/RTO AMOUNT CALCULATOR.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04A6CD18-CC5F-4D2B-A537-4BB00FF54024}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FEB3D8D6-80EA-42CC-A95B-526C9F2832EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{22B1B819-270B-4F63-82EC-34FAFE8739A1}"/>
   </bookViews>
@@ -864,14 +864,14 @@
     </row>
     <row r="5" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="13">
-        <v>656655</v>
+        <v>961449</v>
       </c>
       <c r="B5" s="1">
-        <v>0.18</v>
+        <v>0.4</v>
       </c>
       <c r="C5" s="2">
         <f>A5+(A5*B5)</f>
-        <v>774852.9</v>
+        <v>1346028.6</v>
       </c>
       <c r="D5" s="1">
         <v>0.09</v>
@@ -881,7 +881,7 @@
       </c>
       <c r="F5" s="4">
         <f>C5*D5+E5+664+1.3</f>
-        <v>71902.061000000002</v>
+        <v>123307.87400000001</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -946,7 +946,7 @@
       </c>
       <c r="F10" s="19">
         <f>((C5*F9%)/7.5+1)+664</f>
-        <v>10996.372000000001</v>
+        <v>18612.048000000003</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -966,7 +966,7 @@
       </c>
       <c r="F11" s="21">
         <f>F10+1500</f>
-        <v>12496.372000000001</v>
+        <v>20112.048000000003</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">

--- a/RTO AMOUNT CALCULATOR.xlsx
+++ b/RTO AMOUNT CALCULATOR.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FEB3D8D6-80EA-42CC-A95B-526C9F2832EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{901A6BCA-FE1D-4F26-947F-96327AB550E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{22B1B819-270B-4F63-82EC-34FAFE8739A1}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
   <si>
     <t>RTO AMOUNT CALCULATOR</t>
   </si>
@@ -69,22 +69,10 @@
     <t>RTO (Excl HYP)</t>
   </si>
   <si>
-    <t>IGNIS SIGMA</t>
-  </si>
-  <si>
-    <t>IGNIS DELTA</t>
-  </si>
-  <si>
     <t>FRONX DELTA+</t>
   </si>
   <si>
     <t>BALENO SIGMA</t>
-  </si>
-  <si>
-    <t>IGNIS APLHA</t>
-  </si>
-  <si>
-    <t>IGNIS ZETA</t>
   </si>
   <si>
     <t>BALENO SIGMA©</t>
@@ -864,14 +852,14 @@
     </row>
     <row r="5" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="13">
-        <v>961449</v>
+        <v>656655</v>
       </c>
       <c r="B5" s="1">
-        <v>0.4</v>
+        <v>0.18</v>
       </c>
       <c r="C5" s="2">
         <f>A5+(A5*B5)</f>
-        <v>1346028.6</v>
+        <v>774852.9</v>
       </c>
       <c r="D5" s="1">
         <v>0.09</v>
@@ -881,7 +869,7 @@
       </c>
       <c r="F5" s="4">
         <f>C5*D5+E5+664+1.3</f>
-        <v>123307.87400000001</v>
+        <v>71902.061000000002</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -908,13 +896,13 @@
         <v>62302</v>
       </c>
       <c r="E8" s="30" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="F8" s="30"/>
     </row>
     <row r="9" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="15" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="B9" s="16">
         <v>71902</v>
@@ -924,7 +912,7 @@
         <v>70402</v>
       </c>
       <c r="E9" s="22" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="F9" s="23">
         <v>10</v>
@@ -932,7 +920,7 @@
     </row>
     <row r="10" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="15" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B10" s="16">
         <v>75466</v>
@@ -942,152 +930,118 @@
         <v>73966</v>
       </c>
       <c r="E10" s="18" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="F10" s="19">
         <f>((C5*F9%)/7.5+1)+664</f>
-        <v>18612.048000000003</v>
+        <v>10996.372000000001</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="15" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B11" s="16">
-        <f>50327+14</f>
-        <v>50341</v>
+        <v>56062</v>
       </c>
       <c r="C11" s="15">
-        <f t="shared" si="0"/>
-        <v>48841</v>
+        <f>B11-1500</f>
+        <v>54562</v>
       </c>
       <c r="E11" s="20" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="F11" s="21">
         <f>F10+1500</f>
-        <v>20112.048000000003</v>
+        <v>12496.372000000001</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="15" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B12" s="16">
-        <f>54773+14</f>
-        <v>54787</v>
+        <f>5344+14</f>
+        <v>5358</v>
       </c>
       <c r="C12" s="15">
-        <f t="shared" si="0"/>
-        <v>53287</v>
+        <f>B12-1500</f>
+        <v>3858</v>
       </c>
       <c r="F12" s="17"/>
     </row>
     <row r="13" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="15" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B13" s="16">
-        <v>59557</v>
+        <v>63802</v>
       </c>
       <c r="C13" s="15">
         <f>B13-1500</f>
-        <v>58057</v>
+        <v>62302</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="15" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B14" s="16">
-        <f>64898+14</f>
-        <v>64912</v>
+        <v>71902</v>
       </c>
       <c r="C14" s="15">
-        <f t="shared" si="0"/>
-        <v>63412</v>
+        <f>B14-1500</f>
+        <v>70402</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="15" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="B15" s="16">
-        <v>56062</v>
+        <v>99045</v>
       </c>
       <c r="C15" s="15">
-        <f t="shared" si="0"/>
-        <v>54562</v>
+        <f>B15-1500</f>
+        <v>97545</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="15" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="B16" s="16">
-        <f>5344+14</f>
-        <v>5358</v>
+        <v>111033</v>
       </c>
       <c r="C16" s="15">
-        <f>Table1[[#This Row],[RTO]]-300</f>
-        <v>5058</v>
+        <f>B16-1500</f>
+        <v>109533</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="15" t="s">
-        <v>19</v>
-      </c>
-      <c r="B17" s="16">
-        <v>63802</v>
-      </c>
-      <c r="C17" s="15">
-        <f>Table1[[#This Row],[RTO]]-1500</f>
-        <v>62302</v>
-      </c>
+      <c r="A17" s="15"/>
+      <c r="B17" s="15"/>
+      <c r="C17" s="15"/>
     </row>
     <row r="18" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="15" t="s">
-        <v>20</v>
-      </c>
-      <c r="B18" s="16">
-        <v>71902</v>
-      </c>
-      <c r="C18" s="15">
-        <f>Table1[[#This Row],[RTO]]-1500</f>
-        <v>70402</v>
-      </c>
+      <c r="A18" s="15"/>
+      <c r="B18" s="15"/>
+      <c r="C18" s="15"/>
     </row>
     <row r="19" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="15" t="s">
-        <v>24</v>
-      </c>
-      <c r="B19" s="16">
-        <v>99045</v>
-      </c>
-      <c r="C19" s="15">
-        <f>Table1[[#This Row],[RTO]]-1500</f>
-        <v>97545</v>
-      </c>
+      <c r="A19" s="15"/>
+      <c r="B19" s="15"/>
+      <c r="C19" s="15"/>
     </row>
     <row r="20" spans="1:6" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A20" s="15" t="s">
-        <v>26</v>
-      </c>
-      <c r="B20" s="16">
-        <v>111033</v>
-      </c>
-      <c r="C20" s="15">
-        <f t="shared" ref="C20:C21" si="1">B20-1500</f>
-        <v>109533</v>
-      </c>
+      <c r="A20" s="15"/>
+      <c r="B20" s="15"/>
+      <c r="C20" s="15"/>
     </row>
     <row r="21" spans="1:6" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A21" s="15"/>
       <c r="B21" s="16"/>
-      <c r="C21" s="15">
-        <f t="shared" si="1"/>
-        <v>-1500</v>
-      </c>
+      <c r="C21" s="15"/>
     </row>
     <row r="22" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A22" s="14"/>
@@ -1124,9 +1078,6 @@
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
-  <ignoredErrors>
-    <ignoredError sqref="C16" calculatedColumn="1"/>
-  </ignoredErrors>
   <tableParts count="1">
     <tablePart r:id="rId2"/>
   </tableParts>

--- a/RTO AMOUNT CALCULATOR.xlsx
+++ b/RTO AMOUNT CALCULATOR.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{901A6BCA-FE1D-4F26-947F-96327AB550E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF773AB8-D553-4BFF-922F-E04858DA2DF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{22B1B819-270B-4F63-82EC-34FAFE8739A1}"/>
   </bookViews>
@@ -852,24 +852,24 @@
     </row>
     <row r="5" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="13">
-        <v>656655</v>
+        <v>1003265</v>
       </c>
       <c r="B5" s="1">
         <v>0.18</v>
       </c>
       <c r="C5" s="2">
         <f>A5+(A5*B5)</f>
-        <v>774852.9</v>
+        <v>1183852.7</v>
       </c>
       <c r="D5" s="1">
         <v>0.09</v>
       </c>
       <c r="E5" s="3">
-        <v>1500</v>
+        <v>0</v>
       </c>
       <c r="F5" s="4">
         <f>C5*D5+E5+664+1.3</f>
-        <v>71902.061000000002</v>
+        <v>107212.04299999999</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -926,7 +926,7 @@
         <v>75466</v>
       </c>
       <c r="C10" s="15">
-        <f t="shared" ref="C10:C15" si="0">B10-1500</f>
+        <f t="shared" ref="C10" si="0">B10-1500</f>
         <v>73966</v>
       </c>
       <c r="E10" s="18" t="s">
@@ -934,7 +934,7 @@
       </c>
       <c r="F10" s="19">
         <f>((C5*F9%)/7.5+1)+664</f>
-        <v>10996.372000000001</v>
+        <v>16449.702666666668</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -945,7 +945,7 @@
         <v>56062</v>
       </c>
       <c r="C11" s="15">
-        <f>B11-1500</f>
+        <f t="shared" ref="C11:C16" si="1">B11-1500</f>
         <v>54562</v>
       </c>
       <c r="E11" s="20" t="s">
@@ -953,7 +953,7 @@
       </c>
       <c r="F11" s="21">
         <f>F10+1500</f>
-        <v>12496.372000000001</v>
+        <v>17949.702666666668</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -965,7 +965,7 @@
         <v>5358</v>
       </c>
       <c r="C12" s="15">
-        <f>B12-1500</f>
+        <f t="shared" si="1"/>
         <v>3858</v>
       </c>
       <c r="F12" s="17"/>
@@ -978,7 +978,7 @@
         <v>63802</v>
       </c>
       <c r="C13" s="15">
-        <f>B13-1500</f>
+        <f t="shared" si="1"/>
         <v>62302</v>
       </c>
     </row>
@@ -987,11 +987,11 @@
         <v>16</v>
       </c>
       <c r="B14" s="16">
-        <v>71902</v>
+        <v>73252</v>
       </c>
       <c r="C14" s="15">
-        <f>B14-1500</f>
-        <v>70402</v>
+        <f t="shared" si="1"/>
+        <v>71752</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -1002,7 +1002,7 @@
         <v>99045</v>
       </c>
       <c r="C15" s="15">
-        <f>B15-1500</f>
+        <f t="shared" si="1"/>
         <v>97545</v>
       </c>
     </row>
@@ -1014,7 +1014,7 @@
         <v>111033</v>
       </c>
       <c r="C16" s="15">
-        <f>B16-1500</f>
+        <f t="shared" si="1"/>
         <v>109533</v>
       </c>
     </row>

--- a/RTO AMOUNT CALCULATOR.xlsx
+++ b/RTO AMOUNT CALCULATOR.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF773AB8-D553-4BFF-922F-E04858DA2DF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B31627D6-4813-4A69-A117-9ED64616A9BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{22B1B819-270B-4F63-82EC-34FAFE8739A1}"/>
   </bookViews>
@@ -852,14 +852,14 @@
     </row>
     <row r="5" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="13">
-        <v>1003265</v>
+        <v>580383</v>
       </c>
       <c r="B5" s="1">
         <v>0.18</v>
       </c>
       <c r="C5" s="2">
         <f>A5+(A5*B5)</f>
-        <v>1183852.7</v>
+        <v>684851.94</v>
       </c>
       <c r="D5" s="1">
         <v>0.09</v>
@@ -869,7 +869,7 @@
       </c>
       <c r="F5" s="4">
         <f>C5*D5+E5+664+1.3</f>
-        <v>107212.04299999999</v>
+        <v>62301.974599999994</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -934,7 +934,7 @@
       </c>
       <c r="F10" s="19">
         <f>((C5*F9%)/7.5+1)+664</f>
-        <v>16449.702666666668</v>
+        <v>9796.3592000000008</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -953,7 +953,7 @@
       </c>
       <c r="F11" s="21">
         <f>F10+1500</f>
-        <v>17949.702666666668</v>
+        <v>11296.359200000001</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">

--- a/RTO AMOUNT CALCULATOR.xlsx
+++ b/RTO AMOUNT CALCULATOR.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B31627D6-4813-4A69-A117-9ED64616A9BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9551574-2CA6-4E30-B6C0-DBBBF31E6D98}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{22B1B819-270B-4F63-82EC-34FAFE8739A1}"/>
+    <workbookView xWindow="3135" yWindow="660" windowWidth="20865" windowHeight="12120" xr2:uid="{22B1B819-270B-4F63-82EC-34FAFE8739A1}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -852,24 +852,24 @@
     </row>
     <row r="5" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="13">
-        <v>580383</v>
+        <v>669367</v>
       </c>
       <c r="B5" s="1">
         <v>0.18</v>
       </c>
       <c r="C5" s="2">
         <f>A5+(A5*B5)</f>
-        <v>684851.94</v>
+        <v>789853.06</v>
       </c>
       <c r="D5" s="1">
         <v>0.09</v>
       </c>
       <c r="E5" s="3">
-        <v>0</v>
+        <v>1500</v>
       </c>
       <c r="F5" s="4">
         <f>C5*D5+E5+664+1.3</f>
-        <v>62301.974599999994</v>
+        <v>73252.075400000002</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -934,7 +934,7 @@
       </c>
       <c r="F10" s="19">
         <f>((C5*F9%)/7.5+1)+664</f>
-        <v>9796.3592000000008</v>
+        <v>11196.374133333335</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -953,7 +953,7 @@
       </c>
       <c r="F11" s="21">
         <f>F10+1500</f>
-        <v>11296.359200000001</v>
+        <v>12696.374133333335</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">

--- a/RTO AMOUNT CALCULATOR.xlsx
+++ b/RTO AMOUNT CALCULATOR.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9551574-2CA6-4E30-B6C0-DBBBF31E6D98}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC0C0D57-8D5D-43A9-8E97-BC4925CB6BA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3135" yWindow="660" windowWidth="20865" windowHeight="12120" xr2:uid="{22B1B819-270B-4F63-82EC-34FAFE8739A1}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{22B1B819-270B-4F63-82EC-34FAFE8739A1}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -852,14 +852,14 @@
     </row>
     <row r="5" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="13">
-        <v>669367</v>
+        <v>982103</v>
       </c>
       <c r="B5" s="1">
-        <v>0.18</v>
+        <v>0.4</v>
       </c>
       <c r="C5" s="2">
         <f>A5+(A5*B5)</f>
-        <v>789853.06</v>
+        <v>1374944.2</v>
       </c>
       <c r="D5" s="1">
         <v>0.09</v>
@@ -869,7 +869,7 @@
       </c>
       <c r="F5" s="4">
         <f>C5*D5+E5+664+1.3</f>
-        <v>73252.075400000002</v>
+        <v>125910.27799999999</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -934,7 +934,7 @@
       </c>
       <c r="F10" s="19">
         <f>((C5*F9%)/7.5+1)+664</f>
-        <v>11196.374133333335</v>
+        <v>18997.589333333333</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -953,7 +953,7 @@
       </c>
       <c r="F11" s="21">
         <f>F10+1500</f>
-        <v>12696.374133333335</v>
+        <v>20497.589333333333</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">

--- a/RTO AMOUNT CALCULATOR.xlsx
+++ b/RTO AMOUNT CALCULATOR.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC0C0D57-8D5D-43A9-8E97-BC4925CB6BA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9AA13DD7-B395-4CA4-981D-8C1B0DA65E92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{22B1B819-270B-4F63-82EC-34FAFE8739A1}"/>
   </bookViews>
@@ -852,14 +852,14 @@
     </row>
     <row r="5" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="13">
-        <v>982103</v>
+        <v>586739</v>
       </c>
       <c r="B5" s="1">
-        <v>0.4</v>
+        <v>0.18</v>
       </c>
       <c r="C5" s="2">
         <f>A5+(A5*B5)</f>
-        <v>1374944.2</v>
+        <v>692352.02</v>
       </c>
       <c r="D5" s="1">
         <v>0.09</v>
@@ -869,7 +869,7 @@
       </c>
       <c r="F5" s="4">
         <f>C5*D5+E5+664+1.3</f>
-        <v>125910.27799999999</v>
+        <v>64476.981800000001</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -934,7 +934,7 @@
       </c>
       <c r="F10" s="19">
         <f>((C5*F9%)/7.5+1)+664</f>
-        <v>18997.589333333333</v>
+        <v>9896.3602666666666</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -953,7 +953,7 @@
       </c>
       <c r="F11" s="21">
         <f>F10+1500</f>
-        <v>20497.589333333333</v>
+        <v>11396.360266666667</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -975,11 +975,11 @@
         <v>15</v>
       </c>
       <c r="B13" s="16">
-        <v>63802</v>
+        <v>64477</v>
       </c>
       <c r="C13" s="15">
         <f t="shared" si="1"/>
-        <v>62302</v>
+        <v>62977</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">

--- a/RTO AMOUNT CALCULATOR.xlsx
+++ b/RTO AMOUNT CALCULATOR.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9AA13DD7-B395-4CA4-981D-8C1B0DA65E92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE3FB3EF-C504-4B71-BBFC-F5971A725E54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{22B1B819-270B-4F63-82EC-34FAFE8739A1}"/>
   </bookViews>
@@ -852,14 +852,14 @@
     </row>
     <row r="5" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="13">
-        <v>586739</v>
+        <v>669367</v>
       </c>
       <c r="B5" s="1">
         <v>0.18</v>
       </c>
       <c r="C5" s="2">
         <f>A5+(A5*B5)</f>
-        <v>692352.02</v>
+        <v>789853.06</v>
       </c>
       <c r="D5" s="1">
         <v>0.09</v>
@@ -869,7 +869,7 @@
       </c>
       <c r="F5" s="4">
         <f>C5*D5+E5+664+1.3</f>
-        <v>64476.981800000001</v>
+        <v>73252.075400000002</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -934,7 +934,7 @@
       </c>
       <c r="F10" s="19">
         <f>((C5*F9%)/7.5+1)+664</f>
-        <v>9896.3602666666666</v>
+        <v>11196.374133333335</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -953,7 +953,7 @@
       </c>
       <c r="F11" s="21">
         <f>F10+1500</f>
-        <v>11396.360266666667</v>
+        <v>12696.374133333335</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">

--- a/RTO AMOUNT CALCULATOR.xlsx
+++ b/RTO AMOUNT CALCULATOR.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE3FB3EF-C504-4B71-BBFC-F5971A725E54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8AB0263-6FB7-40D4-BD6D-47A5292053B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{22B1B819-270B-4F63-82EC-34FAFE8739A1}"/>
   </bookViews>
@@ -852,14 +852,14 @@
     </row>
     <row r="5" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="13">
-        <v>669367</v>
+        <v>584620</v>
       </c>
       <c r="B5" s="1">
         <v>0.18</v>
       </c>
       <c r="C5" s="2">
         <f>A5+(A5*B5)</f>
-        <v>789853.06</v>
+        <v>689851.6</v>
       </c>
       <c r="D5" s="1">
         <v>0.09</v>
@@ -869,7 +869,7 @@
       </c>
       <c r="F5" s="4">
         <f>C5*D5+E5+664+1.3</f>
-        <v>73252.075400000002</v>
+        <v>64251.943999999996</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -888,12 +888,11 @@
         <v>7</v>
       </c>
       <c r="B8" s="16">
-        <f>63788+14</f>
-        <v>63802</v>
+        <v>64252</v>
       </c>
       <c r="C8" s="15">
         <f>B8-1500</f>
-        <v>62302</v>
+        <v>62752</v>
       </c>
       <c r="E8" s="30" t="s">
         <v>17</v>
@@ -934,7 +933,7 @@
       </c>
       <c r="F10" s="19">
         <f>((C5*F9%)/7.5+1)+664</f>
-        <v>11196.374133333335</v>
+        <v>9863.021333333334</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -953,7 +952,7 @@
       </c>
       <c r="F11" s="21">
         <f>F10+1500</f>
-        <v>12696.374133333335</v>
+        <v>11363.021333333334</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">

--- a/RTO AMOUNT CALCULATOR.xlsx
+++ b/RTO AMOUNT CALCULATOR.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8AB0263-6FB7-40D4-BD6D-47A5292053B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E0C69A2-AB61-4151-BE3A-D9C9FD933606}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{22B1B819-270B-4F63-82EC-34FAFE8739A1}"/>
   </bookViews>
@@ -852,14 +852,14 @@
     </row>
     <row r="5" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="13">
-        <v>584620</v>
+        <v>992174</v>
       </c>
       <c r="B5" s="1">
-        <v>0.18</v>
+        <v>0.4</v>
       </c>
       <c r="C5" s="2">
         <f>A5+(A5*B5)</f>
-        <v>689851.6</v>
+        <v>1389043.6</v>
       </c>
       <c r="D5" s="1">
         <v>0.09</v>
@@ -869,7 +869,7 @@
       </c>
       <c r="F5" s="4">
         <f>C5*D5+E5+664+1.3</f>
-        <v>64251.943999999996</v>
+        <v>127179.224</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -933,7 +933,7 @@
       </c>
       <c r="F10" s="19">
         <f>((C5*F9%)/7.5+1)+664</f>
-        <v>9863.021333333334</v>
+        <v>19185.581333333335</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -952,7 +952,7 @@
       </c>
       <c r="F11" s="21">
         <f>F10+1500</f>
-        <v>11363.021333333334</v>
+        <v>20685.581333333335</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">

--- a/RTO AMOUNT CALCULATOR.xlsx
+++ b/RTO AMOUNT CALCULATOR.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E0C69A2-AB61-4151-BE3A-D9C9FD933606}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA88E44E-84C6-49DD-88DE-973E897BD0CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{22B1B819-270B-4F63-82EC-34FAFE8739A1}"/>
   </bookViews>
@@ -852,14 +852,14 @@
     </row>
     <row r="5" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="13">
-        <v>992174</v>
+        <v>516824</v>
       </c>
       <c r="B5" s="1">
-        <v>0.4</v>
+        <v>0.18</v>
       </c>
       <c r="C5" s="2">
         <f>A5+(A5*B5)</f>
-        <v>1389043.6</v>
+        <v>609852.31999999995</v>
       </c>
       <c r="D5" s="1">
         <v>0.09</v>
@@ -869,7 +869,7 @@
       </c>
       <c r="F5" s="4">
         <f>C5*D5+E5+664+1.3</f>
-        <v>127179.224</v>
+        <v>57052.008799999996</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -933,7 +933,7 @@
       </c>
       <c r="F10" s="19">
         <f>((C5*F9%)/7.5+1)+664</f>
-        <v>19185.581333333335</v>
+        <v>8796.3642666666674</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -941,18 +941,18 @@
         <v>12</v>
       </c>
       <c r="B11" s="16">
-        <v>56062</v>
+        <v>57052</v>
       </c>
       <c r="C11" s="15">
         <f t="shared" ref="C11:C16" si="1">B11-1500</f>
-        <v>54562</v>
+        <v>55552</v>
       </c>
       <c r="E11" s="20" t="s">
         <v>19</v>
       </c>
       <c r="F11" s="21">
         <f>F10+1500</f>
-        <v>20685.581333333335</v>
+        <v>10296.364266666667</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">

--- a/RTO AMOUNT CALCULATOR.xlsx
+++ b/RTO AMOUNT CALCULATOR.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA88E44E-84C6-49DD-88DE-973E897BD0CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89B59B67-6E70-4BE7-BB17-399FA0B243A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{22B1B819-270B-4F63-82EC-34FAFE8739A1}"/>
   </bookViews>
@@ -852,14 +852,14 @@
     </row>
     <row r="5" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="13">
-        <v>516824</v>
+        <v>584620</v>
       </c>
       <c r="B5" s="1">
         <v>0.18</v>
       </c>
       <c r="C5" s="2">
         <f>A5+(A5*B5)</f>
-        <v>609852.31999999995</v>
+        <v>689851.6</v>
       </c>
       <c r="D5" s="1">
         <v>0.09</v>
@@ -869,7 +869,7 @@
       </c>
       <c r="F5" s="4">
         <f>C5*D5+E5+664+1.3</f>
-        <v>57052.008799999996</v>
+        <v>64251.943999999996</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -933,7 +933,7 @@
       </c>
       <c r="F10" s="19">
         <f>((C5*F9%)/7.5+1)+664</f>
-        <v>8796.3642666666674</v>
+        <v>9863.021333333334</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -952,7 +952,7 @@
       </c>
       <c r="F11" s="21">
         <f>F10+1500</f>
-        <v>10296.364266666667</v>
+        <v>11363.021333333334</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">

--- a/RTO AMOUNT CALCULATOR.xlsx
+++ b/RTO AMOUNT CALCULATOR.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89B59B67-6E70-4BE7-BB17-399FA0B243A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91F15631-9836-4246-90B4-95D502E4C50D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{22B1B819-270B-4F63-82EC-34FAFE8739A1}"/>
   </bookViews>
@@ -852,14 +852,14 @@
     </row>
     <row r="5" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="13">
-        <v>584620</v>
+        <v>804959</v>
       </c>
       <c r="B5" s="1">
         <v>0.18</v>
       </c>
       <c r="C5" s="2">
         <f>A5+(A5*B5)</f>
-        <v>689851.6</v>
+        <v>949851.62</v>
       </c>
       <c r="D5" s="1">
         <v>0.09</v>
@@ -869,7 +869,7 @@
       </c>
       <c r="F5" s="4">
         <f>C5*D5+E5+664+1.3</f>
-        <v>64251.943999999996</v>
+        <v>87651.945800000001</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -933,7 +933,7 @@
       </c>
       <c r="F10" s="19">
         <f>((C5*F9%)/7.5+1)+664</f>
-        <v>9863.021333333334</v>
+        <v>13329.688266666668</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -952,7 +952,7 @@
       </c>
       <c r="F11" s="21">
         <f>F10+1500</f>
-        <v>11363.021333333334</v>
+        <v>14829.688266666668</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">

--- a/RTO AMOUNT CALCULATOR.xlsx
+++ b/RTO AMOUNT CALCULATOR.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91F15631-9836-4246-90B4-95D502E4C50D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2539AA08-1CF2-44AC-AEBC-76D582176FF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{22B1B819-270B-4F63-82EC-34FAFE8739A1}"/>
   </bookViews>
@@ -852,14 +852,14 @@
     </row>
     <row r="5" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="13">
-        <v>804959</v>
+        <v>690213</v>
       </c>
       <c r="B5" s="1">
         <v>0.18</v>
       </c>
       <c r="C5" s="2">
         <f>A5+(A5*B5)</f>
-        <v>949851.62</v>
+        <v>814451.34</v>
       </c>
       <c r="D5" s="1">
         <v>0.09</v>
@@ -869,7 +869,7 @@
       </c>
       <c r="F5" s="4">
         <f>C5*D5+E5+664+1.3</f>
-        <v>87651.945800000001</v>
+        <v>75465.920599999998</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -933,7 +933,7 @@
       </c>
       <c r="F10" s="19">
         <f>((C5*F9%)/7.5+1)+664</f>
-        <v>13329.688266666668</v>
+        <v>11524.351200000001</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -952,7 +952,7 @@
       </c>
       <c r="F11" s="21">
         <f>F10+1500</f>
-        <v>14829.688266666668</v>
+        <v>13024.351200000001</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">

--- a/RTO AMOUNT CALCULATOR.xlsx
+++ b/RTO AMOUNT CALCULATOR.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2539AA08-1CF2-44AC-AEBC-76D582176FF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5CD54AD4-3E02-4136-946C-03B83108A07F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{22B1B819-270B-4F63-82EC-34FAFE8739A1}"/>
   </bookViews>
@@ -852,14 +852,14 @@
     </row>
     <row r="5" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="13">
-        <v>690213</v>
+        <v>593095</v>
       </c>
       <c r="B5" s="1">
         <v>0.18</v>
       </c>
       <c r="C5" s="2">
         <f>A5+(A5*B5)</f>
-        <v>814451.34</v>
+        <v>699852.1</v>
       </c>
       <c r="D5" s="1">
         <v>0.09</v>
@@ -869,7 +869,7 @@
       </c>
       <c r="F5" s="4">
         <f>C5*D5+E5+664+1.3</f>
-        <v>75465.920599999998</v>
+        <v>65151.989000000001</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -933,7 +933,7 @@
       </c>
       <c r="F10" s="19">
         <f>((C5*F9%)/7.5+1)+664</f>
-        <v>11524.351200000001</v>
+        <v>9996.3613333333342</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -952,7 +952,7 @@
       </c>
       <c r="F11" s="21">
         <f>F10+1500</f>
-        <v>13024.351200000001</v>
+        <v>11496.361333333334</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">

--- a/RTO AMOUNT CALCULATOR.xlsx
+++ b/RTO AMOUNT CALCULATOR.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5CD54AD4-3E02-4136-946C-03B83108A07F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C136FD2-FAD3-43D0-81EB-77A112D541CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{22B1B819-270B-4F63-82EC-34FAFE8739A1}"/>
   </bookViews>
@@ -852,14 +852,14 @@
     </row>
     <row r="5" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="13">
-        <v>593095</v>
+        <v>584620</v>
       </c>
       <c r="B5" s="1">
         <v>0.18</v>
       </c>
       <c r="C5" s="2">
         <f>A5+(A5*B5)</f>
-        <v>699852.1</v>
+        <v>689851.6</v>
       </c>
       <c r="D5" s="1">
         <v>0.09</v>
@@ -869,7 +869,7 @@
       </c>
       <c r="F5" s="4">
         <f>C5*D5+E5+664+1.3</f>
-        <v>65151.989000000001</v>
+        <v>64251.943999999996</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -933,7 +933,7 @@
       </c>
       <c r="F10" s="19">
         <f>((C5*F9%)/7.5+1)+664</f>
-        <v>9996.3613333333342</v>
+        <v>9863.021333333334</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -952,7 +952,7 @@
       </c>
       <c r="F11" s="21">
         <f>F10+1500</f>
-        <v>11496.361333333334</v>
+        <v>11363.021333333334</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">

--- a/RTO AMOUNT CALCULATOR.xlsx
+++ b/RTO AMOUNT CALCULATOR.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C136FD2-FAD3-43D0-81EB-77A112D541CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A3BB488-E0BD-4E2B-93FE-38FBAD963117}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{22B1B819-270B-4F63-82EC-34FAFE8739A1}"/>
   </bookViews>

--- a/RTO AMOUNT CALCULATOR.xlsx
+++ b/RTO AMOUNT CALCULATOR.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A3BB488-E0BD-4E2B-93FE-38FBAD963117}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4DA7919-D759-4F76-83B7-D29012F6AF25}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{22B1B819-270B-4F63-82EC-34FAFE8739A1}"/>
   </bookViews>
@@ -852,14 +852,14 @@
     </row>
     <row r="5" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="13">
-        <v>584620</v>
+        <v>899027</v>
       </c>
       <c r="B5" s="1">
         <v>0.18</v>
       </c>
       <c r="C5" s="2">
         <f>A5+(A5*B5)</f>
-        <v>689851.6</v>
+        <v>1060851.8599999999</v>
       </c>
       <c r="D5" s="1">
         <v>0.09</v>
@@ -869,7 +869,7 @@
       </c>
       <c r="F5" s="4">
         <f>C5*D5+E5+664+1.3</f>
-        <v>64251.943999999996</v>
+        <v>97641.967399999994</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -933,7 +933,7 @@
       </c>
       <c r="F10" s="19">
         <f>((C5*F9%)/7.5+1)+664</f>
-        <v>9863.021333333334</v>
+        <v>14809.691466666665</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -952,7 +952,7 @@
       </c>
       <c r="F11" s="21">
         <f>F10+1500</f>
-        <v>11363.021333333334</v>
+        <v>16309.691466666665</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">

--- a/RTO AMOUNT CALCULATOR.xlsx
+++ b/RTO AMOUNT CALCULATOR.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4DA7919-D759-4F76-83B7-D29012F6AF25}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF9B1852-F133-46E7-B583-6A16E481A09F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{22B1B819-270B-4F63-82EC-34FAFE8739A1}"/>
   </bookViews>
@@ -308,7 +308,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="10" fontId="3" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -387,6 +387,7 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -791,7 +792,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CB0C0205-6B62-47CB-815D-5ED05ED4BECA}">
-  <dimension ref="A1:F26"/>
+  <dimension ref="A1:I26"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="23" bestFit="1" customWidth="1"/>
@@ -804,7 +805,7 @@
     <col min="9" max="9" width="13.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="24" t="s">
         <v>0</v>
       </c>
@@ -814,7 +815,7 @@
       <c r="E1" s="25"/>
       <c r="F1" s="26"/>
     </row>
-    <row r="2" spans="1:6" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="27"/>
       <c r="B2" s="28"/>
       <c r="C2" s="28"/>
@@ -822,7 +823,7 @@
       <c r="E2" s="28"/>
       <c r="F2" s="29"/>
     </row>
-    <row r="3" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="8"/>
       <c r="B3" s="9"/>
       <c r="C3" s="9"/>
@@ -830,7 +831,7 @@
       <c r="E3" s="10"/>
       <c r="F3" s="11"/>
     </row>
-    <row r="4" spans="1:6" ht="21" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" ht="21" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
         <v>1</v>
       </c>
@@ -850,16 +851,16 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="13">
-        <v>899027</v>
+        <v>1095472.6000000001</v>
       </c>
       <c r="B5" s="1">
-        <v>0.18</v>
+        <v>0.4</v>
       </c>
       <c r="C5" s="2">
         <f>A5+(A5*B5)</f>
-        <v>1060851.8599999999</v>
+        <v>1533661.6400000001</v>
       </c>
       <c r="D5" s="1">
         <v>0.09</v>
@@ -869,10 +870,10 @@
       </c>
       <c r="F5" s="4">
         <f>C5*D5+E5+664+1.3</f>
-        <v>97641.967399999994</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+        <v>140194.84760000001</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="15" t="s">
         <v>8</v>
       </c>
@@ -883,7 +884,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="15" t="s">
         <v>7</v>
       </c>
@@ -898,8 +899,9 @@
         <v>17</v>
       </c>
       <c r="F8" s="30"/>
-    </row>
-    <row r="9" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="I8" s="31"/>
+    </row>
+    <row r="9" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="15" t="s">
         <v>14</v>
       </c>
@@ -917,7 +919,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="15" t="s">
         <v>11</v>
       </c>
@@ -933,10 +935,10 @@
       </c>
       <c r="F10" s="19">
         <f>((C5*F9%)/7.5+1)+664</f>
-        <v>14809.691466666665</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
+        <v>21113.821866666669</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="15" t="s">
         <v>12</v>
       </c>
@@ -952,10 +954,10 @@
       </c>
       <c r="F11" s="21">
         <f>F10+1500</f>
-        <v>16309.691466666665</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
+        <v>22613.821866666669</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="15" t="s">
         <v>13</v>
       </c>
@@ -969,7 +971,7 @@
       </c>
       <c r="F12" s="17"/>
     </row>
-    <row r="13" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="15" t="s">
         <v>15</v>
       </c>
@@ -981,7 +983,7 @@
         <v>62977</v>
       </c>
     </row>
-    <row r="14" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="15" t="s">
         <v>16</v>
       </c>
@@ -993,7 +995,7 @@
         <v>71752</v>
       </c>
     </row>
-    <row r="15" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="15" t="s">
         <v>20</v>
       </c>
@@ -1005,7 +1007,7 @@
         <v>97545</v>
       </c>
     </row>
-    <row r="16" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="15" t="s">
         <v>22</v>
       </c>

--- a/RTO AMOUNT CALCULATOR.xlsx
+++ b/RTO AMOUNT CALCULATOR.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF9B1852-F133-46E7-B583-6A16E481A09F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99FC65D2-7EA9-47F7-B93A-E484AF183A87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{22B1B819-270B-4F63-82EC-34FAFE8739A1}"/>
   </bookViews>
@@ -366,6 +366,7 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -387,7 +388,6 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -806,22 +806,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="24" t="s">
+      <c r="A1" s="25" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="25"/>
-      <c r="C1" s="25"/>
-      <c r="D1" s="25"/>
-      <c r="E1" s="25"/>
-      <c r="F1" s="26"/>
+      <c r="B1" s="26"/>
+      <c r="C1" s="26"/>
+      <c r="D1" s="26"/>
+      <c r="E1" s="26"/>
+      <c r="F1" s="27"/>
     </row>
     <row r="2" spans="1:9" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="27"/>
-      <c r="B2" s="28"/>
-      <c r="C2" s="28"/>
-      <c r="D2" s="28"/>
-      <c r="E2" s="28"/>
-      <c r="F2" s="29"/>
+      <c r="A2" s="28"/>
+      <c r="B2" s="29"/>
+      <c r="C2" s="29"/>
+      <c r="D2" s="29"/>
+      <c r="E2" s="29"/>
+      <c r="F2" s="30"/>
     </row>
     <row r="3" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="8"/>
@@ -853,14 +853,14 @@
     </row>
     <row r="5" spans="1:9" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="13">
-        <v>1095472.6000000001</v>
+        <v>1412388</v>
       </c>
       <c r="B5" s="1">
         <v>0.4</v>
       </c>
       <c r="C5" s="2">
         <f>A5+(A5*B5)</f>
-        <v>1533661.6400000001</v>
+        <v>1977343.2000000002</v>
       </c>
       <c r="D5" s="1">
         <v>0.09</v>
@@ -870,7 +870,7 @@
       </c>
       <c r="F5" s="4">
         <f>C5*D5+E5+664+1.3</f>
-        <v>140194.84760000001</v>
+        <v>180126.18799999999</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -895,11 +895,11 @@
         <f>B8-1500</f>
         <v>62752</v>
       </c>
-      <c r="E8" s="30" t="s">
+      <c r="E8" s="31" t="s">
         <v>17</v>
       </c>
-      <c r="F8" s="30"/>
-      <c r="I8" s="31"/>
+      <c r="F8" s="31"/>
+      <c r="I8" s="24"/>
     </row>
     <row r="9" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="15" t="s">
@@ -935,7 +935,7 @@
       </c>
       <c r="F10" s="19">
         <f>((C5*F9%)/7.5+1)+664</f>
-        <v>21113.821866666669</v>
+        <v>27029.576000000005</v>
       </c>
     </row>
     <row r="11" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -954,7 +954,7 @@
       </c>
       <c r="F11" s="21">
         <f>F10+1500</f>
-        <v>22613.821866666669</v>
+        <v>28529.576000000005</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">

--- a/RTO AMOUNT CALCULATOR.xlsx
+++ b/RTO AMOUNT CALCULATOR.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99FC65D2-7EA9-47F7-B93A-E484AF183A87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{741ACA9A-9EFA-4A12-9B4D-A79D2299A9E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{22B1B819-270B-4F63-82EC-34FAFE8739A1}"/>
   </bookViews>
@@ -853,14 +853,14 @@
     </row>
     <row r="5" spans="1:9" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="13">
-        <v>1412388</v>
+        <v>760044</v>
       </c>
       <c r="B5" s="1">
-        <v>0.4</v>
+        <v>0.18</v>
       </c>
       <c r="C5" s="2">
         <f>A5+(A5*B5)</f>
-        <v>1977343.2000000002</v>
+        <v>896851.91999999993</v>
       </c>
       <c r="D5" s="1">
         <v>0.09</v>
@@ -870,7 +870,7 @@
       </c>
       <c r="F5" s="4">
         <f>C5*D5+E5+664+1.3</f>
-        <v>180126.18799999999</v>
+        <v>82881.972799999989</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -935,7 +935,7 @@
       </c>
       <c r="F10" s="19">
         <f>((C5*F9%)/7.5+1)+664</f>
-        <v>27029.576000000005</v>
+        <v>12623.025599999999</v>
       </c>
     </row>
     <row r="11" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -954,7 +954,7 @@
       </c>
       <c r="F11" s="21">
         <f>F10+1500</f>
-        <v>28529.576000000005</v>
+        <v>14123.025599999999</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">

--- a/RTO AMOUNT CALCULATOR.xlsx
+++ b/RTO AMOUNT CALCULATOR.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{741ACA9A-9EFA-4A12-9B4D-A79D2299A9E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9F5A8DE-DF81-4E23-B928-D7B7CC3757AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{22B1B819-270B-4F63-82EC-34FAFE8739A1}"/>
   </bookViews>
@@ -853,14 +853,14 @@
     </row>
     <row r="5" spans="1:9" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="13">
-        <v>760044</v>
+        <v>656654</v>
       </c>
       <c r="B5" s="1">
         <v>0.18</v>
       </c>
       <c r="C5" s="2">
         <f>A5+(A5*B5)</f>
-        <v>896851.91999999993</v>
+        <v>774851.72</v>
       </c>
       <c r="D5" s="1">
         <v>0.09</v>
@@ -870,7 +870,7 @@
       </c>
       <c r="F5" s="4">
         <f>C5*D5+E5+664+1.3</f>
-        <v>82881.972799999989</v>
+        <v>71901.954799999992</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -935,7 +935,7 @@
       </c>
       <c r="F10" s="19">
         <f>((C5*F9%)/7.5+1)+664</f>
-        <v>12623.025599999999</v>
+        <v>10996.356266666668</v>
       </c>
     </row>
     <row r="11" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -954,7 +954,7 @@
       </c>
       <c r="F11" s="21">
         <f>F10+1500</f>
-        <v>14123.025599999999</v>
+        <v>12496.356266666668</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">

--- a/RTO AMOUNT CALCULATOR.xlsx
+++ b/RTO AMOUNT CALCULATOR.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9F5A8DE-DF81-4E23-B928-D7B7CC3757AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B270AF73-19F6-4C32-9A5A-E12E75E958F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{22B1B819-270B-4F63-82EC-34FAFE8739A1}"/>
   </bookViews>
@@ -853,14 +853,14 @@
     </row>
     <row r="5" spans="1:9" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="13">
-        <v>656654</v>
+        <v>593095</v>
       </c>
       <c r="B5" s="1">
         <v>0.18</v>
       </c>
       <c r="C5" s="2">
         <f>A5+(A5*B5)</f>
-        <v>774851.72</v>
+        <v>699852.1</v>
       </c>
       <c r="D5" s="1">
         <v>0.09</v>
@@ -870,7 +870,7 @@
       </c>
       <c r="F5" s="4">
         <f>C5*D5+E5+664+1.3</f>
-        <v>71901.954799999992</v>
+        <v>65151.989000000001</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -935,7 +935,7 @@
       </c>
       <c r="F10" s="19">
         <f>((C5*F9%)/7.5+1)+664</f>
-        <v>10996.356266666668</v>
+        <v>9996.3613333333342</v>
       </c>
     </row>
     <row r="11" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -954,7 +954,7 @@
       </c>
       <c r="F11" s="21">
         <f>F10+1500</f>
-        <v>12496.356266666668</v>
+        <v>11496.361333333334</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">

--- a/RTO AMOUNT CALCULATOR.xlsx
+++ b/RTO AMOUNT CALCULATOR.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B270AF73-19F6-4C32-9A5A-E12E75E958F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{329910FB-B40C-4CD8-8D7A-9855CC23AC4A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{22B1B819-270B-4F63-82EC-34FAFE8739A1}"/>
   </bookViews>
@@ -853,14 +853,14 @@
     </row>
     <row r="5" spans="1:9" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="13">
-        <v>593095</v>
+        <v>669369</v>
       </c>
       <c r="B5" s="1">
         <v>0.18</v>
       </c>
       <c r="C5" s="2">
         <f>A5+(A5*B5)</f>
-        <v>699852.1</v>
+        <v>789855.42</v>
       </c>
       <c r="D5" s="1">
         <v>0.09</v>
@@ -870,7 +870,7 @@
       </c>
       <c r="F5" s="4">
         <f>C5*D5+E5+664+1.3</f>
-        <v>65151.989000000001</v>
+        <v>73252.287800000006</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -935,7 +935,7 @@
       </c>
       <c r="F10" s="19">
         <f>((C5*F9%)/7.5+1)+664</f>
-        <v>9996.3613333333342</v>
+        <v>11196.405600000002</v>
       </c>
     </row>
     <row r="11" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -954,7 +954,7 @@
       </c>
       <c r="F11" s="21">
         <f>F10+1500</f>
-        <v>11496.361333333334</v>
+        <v>12696.405600000002</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
